--- a/artfynd/A 56888-2022 artfynd.xlsx
+++ b/artfynd/A 56888-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56888-2022 artfynd.xlsx
+++ b/artfynd/A 56888-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66509385</v>
+        <v>66509383</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421696.215171566</v>
+        <v>421696</v>
       </c>
       <c r="R2" t="n">
-        <v>7050448.197716012</v>
+        <v>7050448</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,19 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66509387</v>
+        <v>66509384</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421293.5279101226</v>
+        <v>421696</v>
       </c>
       <c r="R3" t="n">
-        <v>7050369.020626157</v>
+        <v>7050448</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,21 +849,11 @@
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -895,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>18221</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,19 +883,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66509384</v>
+        <v>66509387</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421696.215171566</v>
+        <v>421294</v>
       </c>
       <c r="R4" t="n">
-        <v>7050448.197716012</v>
+        <v>7050369</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -990,21 +955,11 @@
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1016,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1034,53 +989,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66509383</v>
+        <v>105221881</v>
       </c>
       <c r="B5" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>990</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupsjönskogar, Jmt</t>
+          <t>Djupsjö NV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421696.215171566</v>
+        <v>422185</v>
       </c>
       <c r="R5" t="n">
-        <v>7050448.197716012</v>
+        <v>7049960</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,22 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-09-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-09-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,36 +1078,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>18217</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Johan Råghall, Benny Öwre, Lisa Gideonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66509386</v>
+        <v>105221887</v>
       </c>
       <c r="B6" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,37 +1105,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupsjönskogar, Jmt</t>
+          <t>Djupsjö NV, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421293.5279101226</v>
+        <v>421493</v>
       </c>
       <c r="R6" t="n">
-        <v>7050369.020626157</v>
+        <v>7050441</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,22 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-09-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,36 +1183,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>18220</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Johan Råghall, Benny Öwre, Lisa Gideonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107357718</v>
+        <v>107357705</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421216.5982933233</v>
+        <v>421382</v>
       </c>
       <c r="R7" t="n">
-        <v>7050362.014700037</v>
+        <v>7050382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,19 +1275,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1393,15 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107357717</v>
+        <v>107357706</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1342,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1441,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421631.5954139269</v>
+        <v>421678</v>
       </c>
       <c r="R8" t="n">
-        <v>7050198.437455631</v>
+        <v>7050096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,19 +1385,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1521,12 +1422,7 @@
         <v>107357707</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421719.6316227835</v>
+        <v>421720</v>
       </c>
       <c r="R9" t="n">
-        <v>7050094.649849701</v>
+        <v>7050095</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,19 +1495,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1643,15 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107357719</v>
+        <v>107357710</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421496.5588008269</v>
+        <v>422003</v>
       </c>
       <c r="R10" t="n">
-        <v>7050440.648299085</v>
+        <v>7049957</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,19 +1605,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1768,15 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107357712</v>
+        <v>107357711</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1672,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1816,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421926.4665079587</v>
+        <v>421930</v>
       </c>
       <c r="R11" t="n">
-        <v>7050030.281593022</v>
+        <v>7050021</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,19 +1715,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1893,15 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107357711</v>
+        <v>107357712</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1931,7 +1782,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1941,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421929.8157829407</v>
+        <v>421927</v>
       </c>
       <c r="R12" t="n">
-        <v>7050021.285223413</v>
+        <v>7050030</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,19 +1825,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2018,15 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107357705</v>
+        <v>107357713</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +1892,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2066,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421382.2179690556</v>
+        <v>421708</v>
       </c>
       <c r="R13" t="n">
-        <v>7050382.422117869</v>
+        <v>7050105</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2099,19 +1935,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2146,12 +1972,7 @@
         <v>107357714</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421714.3643756237</v>
+        <v>421714</v>
       </c>
       <c r="R14" t="n">
-        <v>7050134.446237801</v>
+        <v>7050135</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2224,19 +2045,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2271,12 +2082,7 @@
         <v>107357715</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421720.3381778797</v>
+        <v>421720</v>
       </c>
       <c r="R15" t="n">
-        <v>7050141.430032426</v>
+        <v>7050142</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2349,19 +2155,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2393,15 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107357710</v>
+        <v>107357716</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2441,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>422003.2174995458</v>
+        <v>421633</v>
       </c>
       <c r="R16" t="n">
-        <v>7049957.083066907</v>
+        <v>7050192</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2474,19 +2265,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2518,15 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107357713</v>
+        <v>107357717</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2566,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421707.8525994752</v>
+        <v>421631</v>
       </c>
       <c r="R17" t="n">
-        <v>7050105.63680503</v>
+        <v>7050198</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2599,19 +2375,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2643,15 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107357716</v>
+        <v>107357718</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2691,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421633.682578478</v>
+        <v>421217</v>
       </c>
       <c r="R18" t="n">
-        <v>7050192.592104986</v>
+        <v>7050362</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2724,19 +2485,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2768,15 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105221881</v>
+        <v>107357719</v>
       </c>
       <c r="B19" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,16 +2530,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2812,17 +2558,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupsjö NV, Jmt</t>
+          <t>Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>422185.3756590126</v>
+        <v>421497</v>
       </c>
       <c r="R19" t="n">
-        <v>7049959.747113227</v>
+        <v>7050440</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2849,19 +2595,14 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2876,27 +2617,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre, Lisa Gideonsson</t>
+          <t>Benny Öwre, Johan Råghall, Lisa Gideonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105221887</v>
+        <v>107357721</v>
       </c>
       <c r="B20" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,16 +2640,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2921,28 +2657,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Djupsjö NV, Jmt</t>
+          <t>Djupsjö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421493.4590253821</v>
+        <v>422044</v>
       </c>
       <c r="R20" t="n">
-        <v>7050441.61621454</v>
+        <v>7050294</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2969,19 +2705,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2996,77 +2722,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre, Lisa Gideonsson</t>
+          <t>Benny Öwre, Johan Råghall, Lisa Gideonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107357708</v>
+        <v>66509386</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupsjö, Jmt</t>
+          <t>Djupsjönskogar, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>422387.2765512859</v>
+        <v>421294</v>
       </c>
       <c r="R21" t="n">
-        <v>7049729.271068533</v>
+        <v>7050369</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3090,22 +2799,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3116,48 +2815,48 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>18220</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Lisa Gideonsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107357709</v>
+        <v>107357720</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3168,11 +2867,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3180,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>422308.8881526825</v>
+        <v>422305</v>
       </c>
       <c r="R22" t="n">
-        <v>7049736.09021227</v>
+        <v>7049738</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3213,24 +2908,14 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3257,15 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107357720</v>
+        <v>107357708</v>
       </c>
       <c r="B23" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3273,16 +2953,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3290,10 +2970,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3301,10 +2989,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>422304.9171123825</v>
+        <v>422387</v>
       </c>
       <c r="R23" t="n">
-        <v>7049737.970285944</v>
+        <v>7049729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3334,24 +3022,9 @@
           <t>2023-03-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-03-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3375,6 +3048,116 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>107357709</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Djupsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>422309</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7049736</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-03-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-03-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Johan Råghall, Lisa Gideonsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56888-2022 artfynd.xlsx
+++ b/artfynd/A 56888-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66509383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66509384</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66509387</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105221881</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105221887</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357705</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357706</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357707</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357710</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,6 +1796,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357711</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1856,6 +1911,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357712</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357713</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2076,6 +2141,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357714</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2186,6 +2256,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357715</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2296,6 +2371,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357716</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2406,6 +2486,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357717</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2516,6 +2601,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357718</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2626,6 +2716,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357719</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2731,6 +2826,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357721</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2833,6 +2933,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66509386</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2939,6 +3044,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357720</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3048,6 +3158,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357708</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3158,8 +3273,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107357709</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>